--- a/sheets/조재수대금교본/검수/희망가 풀이.xlsx
+++ b/sheets/조재수대금교본/검수/희망가 풀이.xlsx
@@ -1059,7 +1059,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞⊏</t>
+㳞</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -1099,7 +1099,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢ʒ
+          <t xml:space="preserve">潢
 南潢</t>
         </is>
       </c>
@@ -1135,14 +1135,13 @@
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞⊏
+          <t xml:space="preserve">汰㳞
 汰</t>
         </is>
       </c>
@@ -1153,7 +1152,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-潢ʒ</t>
+潢</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -1197,7 +1196,7 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="E14" s="24"/>

--- a/sheets/조재수대금교본/검수/희망가 풀이.xlsx
+++ b/sheets/조재수대금교본/검수/희망가 풀이.xlsx
@@ -1059,7 +1059,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞</t>
+㳞⊏</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -1099,7 +1099,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">潢ʒ
 南潢</t>
         </is>
       </c>
@@ -1141,7 +1141,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">汰㳞⊏
 汰</t>
         </is>
       </c>
@@ -1152,7 +1152,7 @@
       <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-潢</t>
+潢ʒ</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -1196,7 +1196,7 @@
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="E14" s="24"/>

--- a/sheets/조재수대금교본/검수/희망가 풀이.xlsx
+++ b/sheets/조재수대금교본/검수/희망가 풀이.xlsx
@@ -1034,16 +1034,16 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="46.51" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="69.11" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="E3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="69.11" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="69.11" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="69.11" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       <c r="D6" s="21"/>
       <c r="E6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="69.11" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       <c r="D7" s="21"/>
       <c r="E7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="69.11" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="69.11" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="69.11" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -1163,28 +1163,28 @@
       </c>
       <c r="E10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="69.11" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
       <c r="D11" s="21"/>
       <c r="E11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="69.11" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
       <c r="D12" s="21"/>
       <c r="E12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="69.11" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
       <c r="D13" s="21"/>
       <c r="E13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="69.11" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -1207,6 +1207,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
 </worksheet>
 </file>